--- a/satisfaction_surveys/040_nail_strength_serum_testing_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/040_nail_strength_serum_testing_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,8 +973,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_time'}</t>
+          <t>less_than_1_time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 time'}</t>
+          <t>Less than 1 time</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times'}</t>
+          <t>1-2_times</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times'}</t>
+          <t>1-2 times</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_or_more_times'}</t>
+          <t>3_or_more_times</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 or more times'}</t>
+          <t>3 or more times</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very_strong'}</t>
+          <t>very_strong</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Very Strong'}</t>
+          <t>Very Strong</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Weak'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_5_times'}</t>
+          <t>less_than_5_times</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 5 times'}</t>
+          <t>Less than 5 times</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'5-10_times'}</t>
+          <t>5-10_times</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '5-10 times'}</t>
+          <t>5-10 times</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'10-20_times'}</t>
+          <t>10-20_times</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '10-20 times'}</t>
+          <t>10-20 times</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'20+_times'}</t>
+          <t>20+_times</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '20+ times'}</t>
+          <t>20+ times</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'much_easier'}</t>
+          <t>much_easier</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Much easier'}</t>
+          <t>Much easier</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_easier'}</t>
+          <t>slightly_easier</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly easier'}</t>
+          <t>Slightly easier</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'no_difference'}</t>
+          <t>no_difference</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'No difference'}</t>
+          <t>No difference</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_harder'}</t>
+          <t>slightly_harder</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly harder'}</t>
+          <t>Slightly harder</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'much_harder'}</t>
+          <t>much_harder</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Much harder'}</t>
+          <t>Much harder</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'much_faster'}</t>
+          <t>much_faster</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Much faster'}</t>
+          <t>Much faster</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_faster'}</t>
+          <t>slightly_faster</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly faster'}</t>
+          <t>Slightly faster</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'no_difference'}</t>
+          <t>no_difference</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'No difference'}</t>
+          <t>No difference</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_slower'}</t>
+          <t>slightly_slower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly slower'}</t>
+          <t>Slightly slower</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'much_slower'}</t>
+          <t>much_slower</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Much slower'}</t>
+          <t>Much slower</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'faint'}</t>
+          <t>faint</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Faint'}</t>
+          <t>Faint</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_more_sensitive'}</t>
+          <t>slightly_more_sensitive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly more sensitive'}</t>
+          <t>Slightly more sensitive</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'much_more_sensitive'}</t>
+          <t>much_more_sensitive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Much more sensitive'}</t>
+          <t>Much more sensitive</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'vitamin_e'}</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Vitamin E'}</t>
+          <t>Vitamin E</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'calcium'}</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Calcium'}</t>
+          <t>Calcium</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'biotin'}</t>
+          <t>biotin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Biotin'}</t>
+          <t>Biotin</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'too_concentrated'}</t>
+          <t>too_concentrated</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Too concentrated'}</t>
+          <t>Too concentrated</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'too_dilute'}</t>
+          <t>too_dilute</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Too dilute'}</t>
+          <t>Too dilute</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'just_right'}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Just right'}</t>
+          <t>Just right</t>
         </is>
       </c>
     </row>
